--- a/data/Book 2.xlsx
+++ b/data/Book 2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C751286C-2F57-4367-94E4-6337EEF19432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67927B59-A063-4B0E-83E1-476F138E4D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,48 +33,37 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Nombre</t>
   </si>
   <si>
-    <t>Imagen</t>
+    <t>Foto</t>
   </si>
   <si>
-    <t>Alejandro</t>
+    <t>Alfonso de la vega</t>
+  </si>
+  <si>
+    <t>Juan Pérez.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -97,13 +86,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -117,70 +109,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,13 +408,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,13 +423,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="118.5" customHeight="1">
+    <row r="2" spans="1:4" ht="118.5" customHeight="1">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
